--- a/app_data.xlsx
+++ b/app_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17340" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17320" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -419,23 +419,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
-      <c r="B1" t="inlineStr"/>
-      <c r="Z1" t="n">
-        <v>33</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="b">
@@ -446,7 +463,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>こうかなし</t>
         </is>
       </c>
     </row>

--- a/app_data.xlsx
+++ b/app_data.xlsx
@@ -419,51 +419,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>120</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="b">
-        <v>0</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>こうかなし</t>
+          <t>等倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/app_data.xlsx
+++ b/app_data.xlsx
@@ -425,7 +425,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>156</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -437,19 +437,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>150</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,7 +460,7 @@
     </row>
     <row r="4">
       <c r="A4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -476,7 +476,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>等倍</t>
+          <t>かなりいまひとつ</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/app_data.xlsx
+++ b/app_data.xlsx
@@ -419,18 +419,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>120</t>
+      <c r="A1" t="inlineStr"/>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>物理</t>
         </is>
       </c>
     </row>
@@ -440,18 +437,10 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>32</t>
@@ -476,7 +465,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>かなりいまひとつ</t>
+          <t>ばつぐん</t>
         </is>
       </c>
     </row>
